--- a/relay_control_board/BOM.xlsx
+++ b/relay_control_board/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ambadran717/small_projects/relay_control_board/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0322FF14-237B-2C4D-97F2-200FA7C541C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AEAC59-E53E-234C-9A81-C7DC8B187B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
